--- a/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.3.1 Advanced Formulas - HLookup working file.xlsx
+++ b/1.7. EXCEL  SECTION - Advanced Formulas and Functions/1.7.3.1 Advanced Formulas - HLookup working file.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="28810"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/travis/Dropbox/Data Handling in Excel/02 Lookup with HLOOKUP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rittiv/Documents/GitHub/Projects-Data/1.7. EXCEL  SECTION - Advanced Formulas and Functions/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CDC68F-6A54-394E-B0D1-7188F8274A25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10260" yWindow="6300" windowWidth="25600" windowHeight="14400" activeTab="1"/>
+    <workbookView xWindow="25620" yWindow="620" windowWidth="25600" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="marketing_perf" sheetId="6" r:id="rId1"/>
@@ -18,10 +19,21 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">marketing_perf!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="150001" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -1251,13 +1263,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="26" x14ac:knownFonts="1">
     <font>
@@ -1837,7 +1849,7 @@
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1852,35 +1864,35 @@
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="20" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="20" fillId="33" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="22" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="20" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="20" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="22" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="38" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="38" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1888,8 +1900,8 @@
     <xf numFmtId="0" fontId="20" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="36" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="35" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="36" borderId="0" xfId="47" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="1" fillId="36" borderId="0" xfId="48" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
@@ -1945,7 +1957,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Percent" xfId="48" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="48" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -1955,6 +1967,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2246,7 +2261,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M381"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -12334,7 +12349,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:H383">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H383">
     <sortCondition descending="1" ref="G2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12342,7 +12357,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -12428,9 +12443,18 @@
       <c r="L4" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="28"/>
+      <c r="M4" s="26">
+        <f>HLOOKUP(L4,$B$3:$J$9, 4, FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="27">
+        <f>HLOOKUP(L4, $B$3:$J$9, 7,FALSE)</f>
+        <v>2772</v>
+      </c>
+      <c r="O4" s="28">
+        <f>M4/N4</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="29"/>
@@ -12460,9 +12484,18 @@
       <c r="L5" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="28"/>
+      <c r="M5" s="26">
+        <f t="shared" ref="M5:M10" si="0">HLOOKUP(L5,$B$3:$J$9, 4, FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="N5" s="27">
+        <f t="shared" ref="N5:N10" si="1">HLOOKUP(L5, $B$3:$J$9, 7,FALSE)</f>
+        <v>5262</v>
+      </c>
+      <c r="O5" s="28">
+        <f t="shared" ref="O5:O10" si="2">M5/N5</f>
+        <v>2.8506271379703536E-3</v>
+      </c>
     </row>
     <row r="6" spans="1:15" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="29"/>
@@ -12490,9 +12523,18 @@
       <c r="L6" s="18" t="s">
         <v>340</v>
       </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="28"/>
+      <c r="M6" s="26">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+      <c r="N6" s="27">
+        <f t="shared" si="1"/>
+        <v>324</v>
+      </c>
+      <c r="O6" s="28">
+        <f t="shared" si="2"/>
+        <v>0.33950617283950618</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="29"/>
@@ -12516,9 +12558,18 @@
       <c r="L7" s="18" t="s">
         <v>313</v>
       </c>
-      <c r="M7" s="26"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="28"/>
+      <c r="M7" s="26">
+        <f t="shared" si="0"/>
+        <v>3624</v>
+      </c>
+      <c r="N7" s="27">
+        <f t="shared" si="1"/>
+        <v>11481</v>
+      </c>
+      <c r="O7" s="28">
+        <f t="shared" si="2"/>
+        <v>0.31565194669453878</v>
+      </c>
     </row>
     <row r="8" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="29"/>
@@ -12550,9 +12601,18 @@
       <c r="L8" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="M8" s="26"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="28"/>
+      <c r="M8" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="27">
+        <f t="shared" si="1"/>
+        <v>556</v>
+      </c>
+      <c r="O8" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="29"/>
@@ -12586,16 +12646,31 @@
       <c r="L9" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="M9" s="26"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="28"/>
+      <c r="M9" s="26">
+        <f t="shared" si="0"/>
+        <v>2036</v>
+      </c>
+      <c r="N9" s="27">
+        <f t="shared" si="1"/>
+        <v>5727</v>
+      </c>
+      <c r="O9" s="28">
+        <f t="shared" si="2"/>
+        <v>0.35550899249170598</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="L10" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="M10" s="26"/>
-      <c r="N10" s="27"/>
+      <c r="M10" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="27">
+        <f t="shared" si="1"/>
+        <v>321</v>
+      </c>
       <c r="O10" s="28"/>
     </row>
   </sheetData>
